--- a/docs/d/88/inyear.xlsx
+++ b/docs/d/88/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 44 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 43 clubs short</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" s="9" t="n">
         <v>0</v>
@@ -5517,8 +5517,8 @@
       <c r="W47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X47" s="9" t="n">
-        <v>0</v>
+      <c r="X47" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y47" s="9" t="n">
         <v>0</v>
@@ -5622,8 +5622,8 @@
       <c r="W48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X48" s="9" t="n">
-        <v>0</v>
+      <c r="X48" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y48" s="9" t="n">
         <v>0</v>
@@ -5709,7 +5709,7 @@
         <v>0</v>
       </c>
       <c r="S49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" s="9" t="n">
         <v>0</v>
@@ -5723,8 +5723,8 @@
       <c r="W49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X49" s="9" t="n">
-        <v>0</v>
+      <c r="X49" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y49" s="9" t="n">
         <v>0</v>
@@ -5824,8 +5824,8 @@
       <c r="W50" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="X50" s="9" t="n">
-        <v>0</v>
+      <c r="X50" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y50" s="9" t="n">
         <v>0</v>
@@ -5929,8 +5929,8 @@
       <c r="W51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X51" s="9" t="n">
-        <v>0</v>
+      <c r="X51" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y51" s="9" t="n">
         <v>0</v>
@@ -6030,8 +6030,8 @@
       <c r="W52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X52" s="9" t="n">
-        <v>0</v>
+      <c r="X52" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y52" s="9" t="n">
         <v>0</v>
@@ -6136,7 +6136,7 @@
         <v>0</v>
       </c>
       <c r="X53" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y53" s="9" t="n">
         <v>0</v>
@@ -6240,8 +6240,8 @@
       <c r="W54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X54" s="9" t="n">
-        <v>0</v>
+      <c r="X54" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y54" s="9" t="n">
         <v>0</v>
@@ -6345,8 +6345,8 @@
       <c r="W55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X55" s="9" t="n">
-        <v>0</v>
+      <c r="X55" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y55" s="9" t="n">
         <v>0</v>
@@ -6446,8 +6446,8 @@
       <c r="W56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X56" s="9" t="n">
-        <v>0</v>
+      <c r="X56" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y56" s="9" t="n">
         <v>0</v>
@@ -6548,7 +6548,7 @@
         <v>0</v>
       </c>
       <c r="X57" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y57" s="9" t="n">
         <v>0</v>
@@ -6753,8 +6753,8 @@
       <c r="W59" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="X59" s="9" t="n">
-        <v>0</v>
+      <c r="X59" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y59" s="9" t="n">
         <v>0</v>
@@ -6854,8 +6854,8 @@
       <c r="W60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X60" s="9" t="n">
-        <v>0</v>
+      <c r="X60" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y60" s="9" t="n">
         <v>0</v>
@@ -6941,22 +6941,22 @@
         <v>0</v>
       </c>
       <c r="S61" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T61" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T61" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U61" s="10" t="n">
-        <v>1</v>
-      </c>
       <c r="V61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X61" s="9" t="n">
-        <v>0</v>
+      <c r="X61" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y61" s="9" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
         <v>0</v>
       </c>
       <c r="X62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y62" s="9" t="n">
         <v>0</v>
@@ -7158,7 +7158,7 @@
         <v>0</v>
       </c>
       <c r="X63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y63" s="9" t="n">
         <v>0</v>
@@ -7258,8 +7258,8 @@
       <c r="W64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X64" s="9" t="n">
-        <v>0</v>
+      <c r="X64" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y64" s="9" t="n">
         <v>0</v>
@@ -7359,8 +7359,8 @@
       <c r="W65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X65" s="9" t="n">
-        <v>0</v>
+      <c r="X65" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y65" s="9" t="n">
         <v>0</v>
@@ -7464,8 +7464,8 @@
       <c r="W66" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="X66" s="9" t="n">
-        <v>0</v>
+      <c r="X66" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y66" s="9" t="n">
         <v>0</v>
@@ -7569,8 +7569,8 @@
       <c r="W67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X67" s="9" t="n">
-        <v>0</v>
+      <c r="X67" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y67" s="9" t="n">
         <v>0</v>
@@ -14366,7 +14366,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -14380,13 +14380,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
@@ -14424,8 +14424,8 @@
       <c r="U134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V134" s="9" t="n">
-        <v>3</v>
+      <c r="V134" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
@@ -17137,7 +17137,7 @@
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>10</v>
@@ -17207,8 +17207,8 @@
       <c r="Y161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z161" s="9" t="n">
-        <v>0</v>
+      <c r="Z161" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA161" s="10" t="n">
         <v>1</v>
@@ -21889,7 +21889,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -22087,7 +22087,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>

--- a/docs/d/88/inyear.xlsx
+++ b/docs/d/88/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,11 @@
       <c r="AB12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC12" s="4" t="inlineStr"/>
+      <c r="AC12" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -2260,7 +2264,11 @@
       <c r="AB15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2462,7 +2470,11 @@
       <c r="AB17" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC17" s="4" t="inlineStr"/>
+      <c r="AC17" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -2563,7 +2575,11 @@
       <c r="AB18" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC18" s="4" t="inlineStr"/>
+      <c r="AC18" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -3076,7 +3092,11 @@
       <c r="AB23" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC23" s="4" t="inlineStr"/>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -3278,7 +3298,11 @@
       <c r="AB25" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC25" s="4" t="inlineStr"/>
+      <c r="AC25" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -4098,7 +4122,11 @@
       <c r="AB33" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC33" s="4" t="inlineStr"/>
+      <c r="AC33" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -4401,7 +4429,11 @@
       <c r="AB36" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC36" s="4" t="inlineStr"/>
+      <c r="AC36" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -5019,7 +5051,11 @@
       <c r="AB42" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC42" s="4" t="inlineStr"/>
+      <c r="AC42" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -5738,7 +5774,11 @@
       <c r="AB49" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC49" s="4" t="inlineStr"/>
+      <c r="AC49" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -6768,7 +6808,11 @@
       <c r="AB59" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC59" s="4" t="inlineStr"/>
+      <c r="AC59" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -6970,7 +7014,11 @@
       <c r="AB61" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC61" s="4" t="inlineStr"/>
+      <c r="AC61" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -8311,7 +8359,11 @@
       <c r="AB74" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC74" s="4" t="inlineStr"/>
+      <c r="AC74" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -9135,7 +9187,11 @@
       <c r="AB82" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC82" s="4" t="inlineStr"/>
+      <c r="AC82" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -9236,7 +9292,11 @@
       <c r="AB83" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC83" s="4" t="inlineStr"/>
+      <c r="AC83" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -9640,7 +9700,11 @@
       <c r="AB87" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC87" s="4" t="inlineStr"/>
+      <c r="AC87" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -9741,7 +9805,11 @@
       <c r="AB88" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC88" s="4" t="inlineStr"/>
+      <c r="AC88" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -9842,7 +9910,11 @@
       <c r="AB89" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC89" s="4" t="inlineStr"/>
+      <c r="AC89" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -10553,7 +10625,11 @@
       <c r="AB96" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC96" s="4" t="inlineStr"/>
+      <c r="AC96" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -11070,7 +11146,11 @@
       <c r="AB101" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC101" s="4" t="inlineStr"/>
+      <c r="AC101" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -11478,7 +11558,11 @@
       <c r="AB105" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC105" s="4" t="inlineStr"/>
+      <c r="AC105" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -11886,7 +11970,11 @@
       <c r="AB109" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC109" s="4" t="inlineStr"/>
+      <c r="AC109" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -12088,7 +12176,11 @@
       <c r="AB111" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC111" s="4" t="inlineStr"/>
+      <c r="AC111" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -13936,7 +14028,11 @@
       <c r="AB129" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC129" s="4" t="inlineStr"/>
+      <c r="AC129" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -14445,7 +14541,11 @@
       <c r="AB134" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC134" s="4" t="inlineStr"/>
+      <c r="AC134" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -15475,7 +15575,11 @@
       <c r="AB144" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC144" s="4" t="inlineStr"/>
+      <c r="AC144" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -15677,7 +15781,11 @@
       <c r="AB146" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC146" s="4" t="inlineStr"/>
+      <c r="AC146" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -16711,7 +16819,11 @@
       <c r="AB156" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC156" s="4" t="inlineStr"/>
+      <c r="AC156" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -16812,7 +16924,11 @@
       <c r="AB157" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC157" s="4" t="inlineStr"/>
+      <c r="AC157" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
@@ -17014,7 +17130,11 @@
       <c r="AB159" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC159" s="4" t="inlineStr"/>
+      <c r="AC159" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -17426,7 +17546,11 @@
       <c r="AB163" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC163" s="4" t="inlineStr"/>
+      <c r="AC163" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
@@ -17834,7 +17958,11 @@
       <c r="AB167" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC167" s="4" t="inlineStr"/>
+      <c r="AC167" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
@@ -18759,7 +18887,11 @@
       <c r="AB176" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC176" s="4" t="inlineStr"/>
+      <c r="AC176" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
@@ -19373,7 +19505,11 @@
       <c r="AB182" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC182" s="4" t="inlineStr"/>
+      <c r="AC182" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
@@ -19579,7 +19715,11 @@
       <c r="AB184" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC184" s="4" t="inlineStr"/>
+      <c r="AC184" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
@@ -19983,7 +20123,11 @@
       <c r="AB188" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC188" s="4" t="inlineStr"/>
+      <c r="AC188" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
@@ -20490,7 +20634,11 @@
       <c r="AB193" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC193" s="4" t="inlineStr"/>
+      <c r="AC193" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">

--- a/docs/d/88/inyear.xlsx
+++ b/docs/d/88/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 6 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 6 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 40 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 33 clubs short</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -992,14 +992,14 @@
       <c r="P3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" s="9" t="n">
-        <v>1</v>
+      <c r="Q3" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R3" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" s="9" t="n">
         <v>0</v>
@@ -1892,13 +1892,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>4</v>
       </c>
       <c r="W12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12" s="10" t="n">
         <v>7</v>
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2035,8 +2035,8 @@
       <c r="S13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T13" s="9" t="n">
-        <v>0</v>
+      <c r="T13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U13" s="9" t="n">
         <v>0</v>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>4</v>
       </c>
       <c r="W14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>5</v>
@@ -2720,13 +2720,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4218,8 +4218,8 @@
       <c r="Y34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z34" s="9" t="n">
-        <v>0</v>
+      <c r="Z34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA34" s="10" t="n">
         <v>1</v>
@@ -4319,8 +4319,8 @@
       <c r="Y35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z35" s="9" t="n">
-        <v>0</v>
+      <c r="Z35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA35" s="9" t="n">
         <v>0</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6391,8 +6391,8 @@
       <c r="Y55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z55" s="9" t="n">
-        <v>0</v>
+      <c r="Z55" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA55" s="10" t="n">
         <v>1</v>
@@ -6834,7 +6834,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6904,8 +6904,8 @@
       <c r="Y60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z60" s="9" t="n">
-        <v>0</v>
+      <c r="Z60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA60" s="10" t="n">
         <v>1</v>
@@ -6935,7 +6935,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6949,13 +6949,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -6993,11 +6993,11 @@
       <c r="U61" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V61" s="9" t="n">
-        <v>3</v>
+      <c r="V61" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X61" s="10" t="n">
         <v>5</v>
@@ -8393,13 +8393,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>4</v>
       </c>
       <c r="W75" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X75" s="10" t="n">
         <v>7</v>
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="P77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q77" s="9" t="n">
         <v>0</v>
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9355,8 +9355,8 @@
       <c r="P84" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q84" s="9" t="n">
-        <v>1</v>
+      <c r="Q84" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R84" s="9" t="n">
         <v>0</v>
@@ -9734,13 +9734,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
         </is>
       </c>
       <c r="P100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q100" s="9" t="n">
         <v>0</v>
@@ -11990,7 +11990,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -12004,13 +12004,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -12048,8 +12048,8 @@
       <c r="U110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V110" s="9" t="n">
-        <v>3</v>
+      <c r="V110" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -12109,17 +12109,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L111" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>6</v>
+      </c>
+      <c r="L111" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M111" s="8" t="n">
@@ -12157,7 +12157,7 @@
         <v>4</v>
       </c>
       <c r="W111" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X111" s="10" t="n">
         <v>5</v>
@@ -12612,7 +12612,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12626,17 +12626,17 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L116" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L116" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M116" s="8" t="n">
@@ -12670,11 +12670,11 @@
       <c r="U116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V116" s="9" t="n">
-        <v>2</v>
+      <c r="V116" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X116" s="9" t="n">
         <v>0</v>
@@ -14575,13 +14575,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>4</v>
       </c>
       <c r="W135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X135" s="9" t="n">
         <v>0</v>
@@ -14771,7 +14771,7 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14785,10 +14785,10 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K137" s="4" t="n">
         <v>0</v>
@@ -14841,8 +14841,8 @@
       <c r="Y137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z137" s="9" t="n">
-        <v>0</v>
+      <c r="Z137" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA137" s="10" t="n">
         <v>1</v>
@@ -16433,13 +16433,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>4</v>
       </c>
       <c r="W153" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X153" s="10" t="n">
         <v>5</v>
@@ -17150,7 +17150,7 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -17194,13 +17194,13 @@
         <v>0</v>
       </c>
       <c r="Q160" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S160" s="9" t="n">
-        <v>1</v>
+      <c r="S160" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T160" s="9" t="n">
         <v>0</v>
@@ -17255,7 +17255,7 @@
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>10</v>
@@ -17325,8 +17325,8 @@
       <c r="Y161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z161" s="9" t="n">
-        <v>0</v>
+      <c r="Z161" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA161" s="10" t="n">
         <v>1</v>
@@ -17566,7 +17566,7 @@
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>10</v>
@@ -17618,8 +17618,8 @@
       <c r="S164" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T164" s="9" t="n">
-        <v>0</v>
+      <c r="T164" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U164" s="9" t="n">
         <v>0</v>
@@ -18097,13 +18097,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>4</v>
       </c>
       <c r="W169" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X169" s="10" t="n">
         <v>5</v>
@@ -18390,7 +18390,7 @@
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F172" s="6" t="n">
         <v>10</v>
@@ -18460,8 +18460,8 @@
       <c r="Y172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z172" s="9" t="n">
-        <v>0</v>
+      <c r="Z172" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA172" s="10" t="n">
         <v>1</v>
@@ -18697,7 +18697,7 @@
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -18711,13 +18711,13 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L175" s="4" t="inlineStr">
         <is>
@@ -18755,11 +18755,11 @@
       <c r="U175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V175" s="9" t="n">
-        <v>3</v>
+      <c r="V175" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W175" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X175" s="10" t="n">
         <v>4</v>
@@ -20190,7 +20190,7 @@
         <v>2</v>
       </c>
       <c r="R189" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S189" s="9" t="n">
         <v>0</v>
@@ -21344,7 +21344,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -21377,7 +21377,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -21509,7 +21509,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -21641,7 +21641,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -21674,13 +21674,13 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -21806,13 +21806,13 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -21971,7 +21971,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -22019,7 +22019,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -22037,7 +22037,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -22052,7 +22052,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -22169,7 +22169,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -22334,7 +22334,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -22367,7 +22367,7 @@
         <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -22433,7 +22433,7 @@
         <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>

--- a/docs/d/88/inyear.xlsx
+++ b/docs/d/88/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/88/inyear.xlsx
+++ b/docs/d/88/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/88/inyear.xlsx
+++ b/docs/d/88/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/88/inyear.xlsx
+++ b/docs/d/88/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/88/inyear.xlsx
+++ b/docs/d/88/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 6 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 6 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 33 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 33 clubs short</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>4</v>
       </c>
       <c r="W10" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X10" s="10" t="n">
         <v>4</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1825,8 +1825,8 @@
       <c r="S11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T11" s="9" t="n">
-        <v>0</v>
+      <c r="T11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U11" s="9" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2038,8 +2038,8 @@
       <c r="T13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U13" s="9" t="n">
-        <v>0</v>
+      <c r="U13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V13" s="10" t="n">
         <v>4</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="P22" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="9" t="n">
         <v>1</v>
@@ -4391,7 +4391,7 @@
         </is>
       </c>
       <c r="P36" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q36" s="9" t="n">
         <v>0</v>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -6020,17 +6020,17 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L52" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M52" s="8" t="n">
@@ -6064,8 +6064,8 @@
       <c r="U52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V52" s="9" t="n">
-        <v>3</v>
+      <c r="V52" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W52" s="9" t="n">
         <v>0</v>
@@ -6335,13 +6335,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>4</v>
       </c>
       <c r="W55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X55" s="10" t="n">
         <v>4</v>
@@ -7054,13 +7054,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8189,13 +8189,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -8233,11 +8233,11 @@
       <c r="U73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V73" s="9" t="n">
+      <c r="V73" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W73" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="W73" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X73" s="10" t="n">
         <v>6</v>
@@ -8758,8 +8758,8 @@
       <c r="W78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X78" s="9" t="n">
-        <v>3</v>
+      <c r="X78" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y78" s="9" t="n">
         <v>0</v>
@@ -9326,13 +9326,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>4</v>
       </c>
       <c r="W84" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X84" s="10" t="n">
         <v>5</v>
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         </is>
       </c>
       <c r="P97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q97" s="9" t="n">
         <v>0</v>
@@ -11075,13 +11075,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>4</v>
       </c>
       <c r="W101" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X101" s="10" t="n">
         <v>7</v>
@@ -11285,13 +11285,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>4</v>
       </c>
       <c r="W103" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X103" s="10" t="n">
         <v>7</v>
@@ -11578,7 +11578,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11619,16 +11619,16 @@
         </is>
       </c>
       <c r="P106" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q106" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q106" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S106" s="9" t="n">
-        <v>1</v>
+      <c r="S106" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="T106" s="10" t="n">
         <v>1</v>
@@ -11831,10 +11831,10 @@
         <v>2</v>
       </c>
       <c r="R108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T108" s="9" t="n">
         <v>0</v>
@@ -12725,13 +12725,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14773,13 +14773,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
@@ -14799,8 +14799,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P137" s="9" t="n">
-        <v>3</v>
+      <c r="P137" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q137" s="10" t="n">
         <v>2</v>
@@ -14821,7 +14821,7 @@
         <v>4</v>
       </c>
       <c r="W137" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X137" s="9" t="n">
         <v>0</v>
@@ -15189,17 +15189,17 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L141" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L141" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M141" s="8" t="n">
@@ -15237,7 +15237,7 @@
         <v>4</v>
       </c>
       <c r="W141" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X141" s="10" t="n">
         <v>5</v>
@@ -16526,13 +16526,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L154" s="7" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>0</v>
       </c>
       <c r="V154" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W154" s="9" t="n">
         <v>0</v>
@@ -16778,7 +16778,7 @@
         <v>1</v>
       </c>
       <c r="U156" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V156" s="10" t="n">
         <v>4</v>
@@ -17183,7 +17183,7 @@
         </is>
       </c>
       <c r="P160" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q160" s="9" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         </is>
       </c>
       <c r="P164" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q164" s="9" t="n">
         <v>1</v>
@@ -17703,7 +17703,7 @@
         <v>0</v>
       </c>
       <c r="Q165" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R165" s="9" t="n">
         <v>0</v>
@@ -17869,7 +17869,7 @@
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -17883,13 +17883,13 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L167" s="4" t="inlineStr">
         <is>
@@ -17930,8 +17930,8 @@
       <c r="V167" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W167" s="9" t="n">
-        <v>3</v>
+      <c r="W167" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X167" s="10" t="n">
         <v>4</v>
@@ -18018,7 +18018,7 @@
         <v>1</v>
       </c>
       <c r="Q168" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R168" s="9" t="n">
         <v>0</v>
@@ -18176,7 +18176,7 @@
         </is>
       </c>
       <c r="E170" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F170" s="6" t="n">
         <v>10</v>
@@ -18190,13 +18190,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L170" s="7" t="inlineStr">
         <is>
@@ -18222,8 +18222,8 @@
       <c r="Q170" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R170" s="9" t="n">
-        <v>1</v>
+      <c r="R170" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S170" s="9" t="n">
         <v>0</v>
@@ -18703,13 +18703,13 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>0</v>
       </c>
       <c r="V175" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W175" s="9" t="n">
         <v>0</v>
@@ -19014,13 +19014,13 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L178" s="7" t="inlineStr">
         <is>
@@ -19426,13 +19426,13 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L182" s="7" t="inlineStr">
         <is>
@@ -19737,13 +19737,13 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J185" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L185" s="4" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>0</v>
       </c>
       <c r="S185" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T185" s="10" t="n">
         <v>1</v>
@@ -19785,7 +19785,7 @@
         <v>4</v>
       </c>
       <c r="W185" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X185" s="10" t="n">
         <v>4</v>
@@ -21102,7 +21102,7 @@
         <v>0</v>
       </c>
       <c r="Q198" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R198" s="9" t="n">
         <v>0</v>
@@ -21575,7 +21575,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -21839,7 +21839,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -21854,7 +21854,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -21938,7 +21938,7 @@
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -22169,7 +22169,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -22334,7 +22334,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -22382,7 +22382,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -22565,7 +22565,7 @@
         <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -22598,7 +22598,7 @@
         <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>

--- a/docs/d/88/inyear.xlsx
+++ b/docs/d/88/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 6 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 6 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 33 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 33 clubs short</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1720,8 +1720,8 @@
       <c r="S10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T10" s="9" t="n">
-        <v>0</v>
+      <c r="T10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U10" s="9" t="n">
         <v>0</v>
@@ -3132,13 +3132,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -4162,13 +4162,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>4</v>
       </c>
       <c r="W34" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X34" s="10" t="n">
         <v>4</v>
@@ -4917,7 +4917,7 @@
         <v>0</v>
       </c>
       <c r="S41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T41" s="9" t="n">
         <v>0</v>
@@ -6729,7 +6729,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6769,8 +6769,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P59" s="9" t="n">
-        <v>2</v>
+      <c r="P59" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q59" s="9" t="n">
         <v>1</v>
@@ -6779,10 +6779,10 @@
         <v>0</v>
       </c>
       <c r="S59" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U59" s="9" t="n">
         <v>0</v>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="P61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q61" s="9" t="n">
         <v>1</v>
@@ -7462,17 +7462,17 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L66" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M66" s="8" t="n">
@@ -7510,7 +7510,7 @@
         <v>4</v>
       </c>
       <c r="W66" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X66" s="10" t="n">
         <v>4</v>
@@ -8084,13 +8084,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>4</v>
       </c>
       <c r="W72" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X72" s="10" t="n">
         <v>7</v>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8189,13 +8189,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -8236,8 +8236,8 @@
       <c r="V73" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W73" s="9" t="n">
-        <v>3</v>
+      <c r="W73" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X73" s="10" t="n">
         <v>6</v>
@@ -8423,7 +8423,7 @@
         <v>0</v>
       </c>
       <c r="Q75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" s="9" t="n">
         <v>0</v>
@@ -10659,13 +10659,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
@@ -11625,7 +11625,7 @@
         <v>2</v>
       </c>
       <c r="R106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S106" s="10" t="n">
         <v>3</v>
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12136,7 +12136,7 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q111" s="9" t="n">
         <v>0</v>
@@ -12147,8 +12147,8 @@
       <c r="S111" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T111" s="9" t="n">
-        <v>0</v>
+      <c r="T111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U111" s="9" t="n">
         <v>0</v>
@@ -12240,7 +12240,7 @@
         <v>0</v>
       </c>
       <c r="Q112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R112" s="9" t="n">
         <v>0</v>
@@ -12505,7 +12505,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12560,8 +12560,8 @@
       <c r="T115" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U115" s="9" t="n">
-        <v>0</v>
+      <c r="U115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V115" s="9" t="n">
         <v>2</v>
@@ -16104,7 +16104,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -16118,13 +16118,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L150" s="7" t="inlineStr">
         <is>
@@ -16162,8 +16162,8 @@
       <c r="U150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V150" s="9" t="n">
-        <v>3</v>
+      <c r="V150" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W150" s="9" t="n">
         <v>0</v>
@@ -16512,7 +16512,7 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -16526,13 +16526,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L154" s="7" t="inlineStr">
         <is>
@@ -16570,8 +16570,8 @@
       <c r="U154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V154" s="9" t="n">
-        <v>3</v>
+      <c r="V154" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W154" s="9" t="n">
         <v>0</v>
@@ -16661,13 +16661,13 @@
         <v>0</v>
       </c>
       <c r="Q155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R155" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T155" s="9" t="n">
         <v>0</v>
@@ -17078,7 +17078,7 @@
         </is>
       </c>
       <c r="P159" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q159" s="9" t="n">
         <v>0</v>
@@ -17389,7 +17389,7 @@
         </is>
       </c>
       <c r="P162" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q162" s="9" t="n">
         <v>1</v>
@@ -17805,7 +17805,7 @@
         </is>
       </c>
       <c r="P166" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q166" s="9" t="n">
         <v>0</v>
@@ -18217,7 +18217,7 @@
         </is>
       </c>
       <c r="P170" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q170" s="10" t="n">
         <v>2</v>
@@ -18909,13 +18909,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>4</v>
       </c>
       <c r="W177" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X177" s="10" t="n">
         <v>4</v>
@@ -19119,17 +19119,17 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L179" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L179" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M179" s="8" t="n">
@@ -19167,7 +19167,7 @@
         <v>4</v>
       </c>
       <c r="W179" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X179" s="10" t="n">
         <v>6</v>
@@ -21163,7 +21163,7 @@
         </is>
       </c>
       <c r="E199" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F199" s="6" t="n">
         <v>10</v>
@@ -21218,8 +21218,8 @@
       <c r="T199" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U199" s="9" t="n">
-        <v>0</v>
+      <c r="U199" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V199" s="9" t="n">
         <v>1</v>
@@ -21575,13 +21575,13 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -21872,7 +21872,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -21920,7 +21920,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -21938,7 +21938,7 @@
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -22202,7 +22202,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -22433,7 +22433,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -22466,7 +22466,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -22646,7 +22646,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -22796,7 +22796,7 @@
         <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
